--- a/재정학/07_Reference/재정학 데이터.xlsx
+++ b/재정학/07_Reference/재정학 데이터.xlsx
@@ -8,15 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\07_Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A982495B-9A3A-475E-9E01-4486A728410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9196A6EA-8A76-44D0-B441-0CA364065CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{F71892C6-1444-47C4-A64C-0935CCB8F15B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="711" activeTab="9" xr2:uid="{F71892C6-1444-47C4-A64C-0935CCB8F15B}"/>
   </bookViews>
   <sheets>
     <sheet name="재정규모" sheetId="3" r:id="rId1"/>
     <sheet name="국세수입" sheetId="1" r:id="rId2"/>
     <sheet name="세외수입" sheetId="2" r:id="rId3"/>
+    <sheet name="기능별 세출실적" sheetId="4" r:id="rId4"/>
+    <sheet name="성질별 분류" sheetId="5" r:id="rId5"/>
+    <sheet name="국가별 재정지출규모" sheetId="6" r:id="rId6"/>
+    <sheet name="공공사회복지 지출 수준 비교" sheetId="7" r:id="rId7"/>
+    <sheet name="기능별 세출 (연도별)" sheetId="8" r:id="rId8"/>
+    <sheet name="조세부담률 변화 추이" sheetId="9" r:id="rId9"/>
+    <sheet name="지방재정" sheetId="10" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="464">
   <si>
     <t>내국세</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -520,6 +530,959 @@
   <si>
     <t>연차별 통합재정규모</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산현액</t>
+  </si>
+  <si>
+    <t>지출액</t>
+  </si>
+  <si>
+    <t>일반·지방행정</t>
+  </si>
+  <si>
+    <t>공공질서및안전</t>
+  </si>
+  <si>
+    <t>통일·외교</t>
+  </si>
+  <si>
+    <t>국방</t>
+  </si>
+  <si>
+    <t>교육</t>
+  </si>
+  <si>
+    <t>문화및관광</t>
+  </si>
+  <si>
+    <t>환경</t>
+  </si>
+  <si>
+    <t>사회복지</t>
+  </si>
+  <si>
+    <t>보건</t>
+  </si>
+  <si>
+    <t>농림수산</t>
+  </si>
+  <si>
+    <t>산업·중소기업및에너지</t>
+  </si>
+  <si>
+    <t>교통및물류</t>
+  </si>
+  <si>
+    <t>통신</t>
+  </si>
+  <si>
+    <t>국토및지역개발</t>
+  </si>
+  <si>
+    <t>과학기술</t>
+  </si>
+  <si>
+    <t>예비비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출처: 2024회계연도 결산개요 (통계편), 기획재정부, </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4) 기능별 세출실적 (16쪽)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구성비(%)</t>
+  </si>
+  <si>
+    <t>2023결산</t>
+  </si>
+  <si>
+    <t>예산현액대비증감(A-B)</t>
+  </si>
+  <si>
+    <t>D/A(%)</t>
+  </si>
+  <si>
+    <t>전년대비증감(B-C)</t>
+  </si>
+  <si>
+    <t>E/C(%)</t>
+  </si>
+  <si>
+    <t>지출액 ranking</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구성비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Top5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024지출</t>
+  </si>
+  <si>
+    <t>인건비</t>
+  </si>
+  <si>
+    <t>물건비</t>
+  </si>
+  <si>
+    <t>운영비</t>
+  </si>
+  <si>
+    <t>여비</t>
+  </si>
+  <si>
+    <t>특수활동비</t>
+  </si>
+  <si>
+    <t>업무추진비</t>
+  </si>
+  <si>
+    <t>직무수행경비</t>
+  </si>
+  <si>
+    <t>연구용역비</t>
+  </si>
+  <si>
+    <t>안보비</t>
+  </si>
+  <si>
+    <t>정보보안비</t>
+  </si>
+  <si>
+    <t>이전지출</t>
+  </si>
+  <si>
+    <t>보전금</t>
+  </si>
+  <si>
+    <t>민간이전</t>
+  </si>
+  <si>
+    <t>자치단체이전</t>
+  </si>
+  <si>
+    <t>해외이전</t>
+  </si>
+  <si>
+    <t>일반출연금</t>
+  </si>
+  <si>
+    <t>연구개발출연금</t>
+  </si>
+  <si>
+    <t>자산취득</t>
+  </si>
+  <si>
+    <t>건설보상비</t>
+  </si>
+  <si>
+    <t>건설비</t>
+  </si>
+  <si>
+    <t>유형자산</t>
+  </si>
+  <si>
+    <t>무형자산</t>
+  </si>
+  <si>
+    <t>융자금</t>
+  </si>
+  <si>
+    <t>출자금</t>
+  </si>
+  <si>
+    <t>예탁금</t>
+  </si>
+  <si>
+    <t>지분취득비</t>
+  </si>
+  <si>
+    <t>상환지출</t>
+  </si>
+  <si>
+    <t>전출금</t>
+  </si>
+  <si>
+    <t>예비비및기타</t>
+  </si>
+  <si>
+    <t>예산현액대비증감</t>
+  </si>
+  <si>
+    <t>증감률D/A(%)</t>
+  </si>
+  <si>
+    <t>전년대비증감</t>
+  </si>
+  <si>
+    <t>전년대비증가율E/C(%)</t>
+  </si>
+  <si>
+    <t>4) 기능별 세출실적 (18쪽)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.openfiscaldata.go.kr/op/ko/ug/UOPKOUGA03?ctzAcctStatsAmtDivCd=SNA02&amp;statsYrFr=2023&amp;statsYrTo=2023&amp;langCd=ko</t>
+  </si>
+  <si>
+    <t>프랑스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이탈리아</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포르투갈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>영국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스웨덴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>독일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.nabo.go.kr/board/file/bulkDown.do?idx=9157&amp;bid=68</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국회예산정책처, 나보포커스, 제 141호 (2026.03.1) 국제 비교로 본 한국 복지지출 수준과 신규 과제 (안태훈 분석관)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>세입규모</t>
+  </si>
+  <si>
+    <t>조세</t>
+  </si>
+  <si>
+    <t>내국세</t>
+  </si>
+  <si>
+    <t>관세</t>
+  </si>
+  <si>
+    <t>방위세</t>
+  </si>
+  <si>
+    <t>교통세</t>
+  </si>
+  <si>
+    <t>교육세</t>
+  </si>
+  <si>
+    <t>종합부동산세</t>
+  </si>
+  <si>
+    <t>세외수입</t>
+  </si>
+  <si>
+    <t>차관수입</t>
+  </si>
+  <si>
+    <t>국공채및차입금</t>
+  </si>
+  <si>
+    <t>세출규모</t>
+  </si>
+  <si>
+    <t>일반지방행정</t>
+  </si>
+  <si>
+    <t>통일외교</t>
+  </si>
+  <si>
+    <t>산업중소기업및에너지</t>
+  </si>
+  <si>
+    <t>국방</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사회복지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>교육</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 한국은행 신계열 GDP 기준(2015년에서 2020년으로 기준년 개편)</t>
+  </si>
+  <si>
+    <t>주석:</t>
+  </si>
+  <si>
+    <t>* GDP : 한국은행, 25.6월 발표 국민계정 자료(신계열 기준, 2020년)</t>
+  </si>
+  <si>
+    <t>* 국세, 지방세 실적 : 국세청.관세청「징수보고서」, 행정안전부「지방세 통계연감」</t>
+  </si>
+  <si>
+    <t>출처:</t>
+  </si>
+  <si>
+    <t>114.1</t>
+  </si>
+  <si>
+    <t>112.5</t>
+  </si>
+  <si>
+    <t>118.6</t>
+  </si>
+  <si>
+    <t>112.8</t>
+  </si>
+  <si>
+    <t>102.0</t>
+  </si>
+  <si>
+    <t>90.5</t>
+  </si>
+  <si>
+    <t>84.3</t>
+  </si>
+  <si>
+    <t>80.4</t>
+  </si>
+  <si>
+    <t>75.5</t>
+  </si>
+  <si>
+    <t>71.0</t>
+  </si>
+  <si>
+    <t>61.7</t>
+  </si>
+  <si>
+    <t>53.8</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>49.2</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>45.5</t>
+  </si>
+  <si>
+    <t>43.4</t>
+  </si>
+  <si>
+    <t>41.3</t>
+  </si>
+  <si>
+    <t>36.0</t>
+  </si>
+  <si>
+    <t>34.2</t>
+  </si>
+  <si>
+    <t>33.1</t>
+  </si>
+  <si>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>26.7</t>
+  </si>
+  <si>
+    <t>20.6</t>
+  </si>
+  <si>
+    <t>18.6</t>
+  </si>
+  <si>
+    <t>17.1</t>
+  </si>
+  <si>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>17.4</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>지방세</t>
+  </si>
+  <si>
+    <t>336.5</t>
+  </si>
+  <si>
+    <t>344.1</t>
+  </si>
+  <si>
+    <t>395.9</t>
+  </si>
+  <si>
+    <t>285.5</t>
+  </si>
+  <si>
+    <t>293.5</t>
+  </si>
+  <si>
+    <t>293.6</t>
+  </si>
+  <si>
+    <t>265.4</t>
+  </si>
+  <si>
+    <t>242.6</t>
+  </si>
+  <si>
+    <t>217.9</t>
+  </si>
+  <si>
+    <t>205.5</t>
+  </si>
+  <si>
+    <t>201.9</t>
+  </si>
+  <si>
+    <t>203.0</t>
+  </si>
+  <si>
+    <t>192.4</t>
+  </si>
+  <si>
+    <t>177.7</t>
+  </si>
+  <si>
+    <t>164.5</t>
+  </si>
+  <si>
+    <t>167.3</t>
+  </si>
+  <si>
+    <t>161.4</t>
+  </si>
+  <si>
+    <t>138.0</t>
+  </si>
+  <si>
+    <t>127.5</t>
+  </si>
+  <si>
+    <t>117.8</t>
+  </si>
+  <si>
+    <t>114.7</t>
+  </si>
+  <si>
+    <t>104.0</t>
+  </si>
+  <si>
+    <t>95.8</t>
+  </si>
+  <si>
+    <t>92.9</t>
+  </si>
+  <si>
+    <t>75.7</t>
+  </si>
+  <si>
+    <t>67.8</t>
+  </si>
+  <si>
+    <t>69.9</t>
+  </si>
+  <si>
+    <t>65.0</t>
+  </si>
+  <si>
+    <t>56.8</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>39.3</t>
+  </si>
+  <si>
+    <t>35.2</t>
+  </si>
+  <si>
+    <t>30.3</t>
+  </si>
+  <si>
+    <t>26.8</t>
+  </si>
+  <si>
+    <t>국세</t>
+  </si>
+  <si>
+    <t>17.6</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>22.1</t>
+  </si>
+  <si>
+    <t>18.8</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>16.6</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>16.9</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>17.2</t>
+  </si>
+  <si>
+    <t>16.1</t>
+  </si>
+  <si>
+    <t>17.0</t>
+  </si>
+  <si>
+    <t>16.8</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>15.8</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>15.9</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>15.6</t>
+  </si>
+  <si>
+    <t>(조세부담률,%)</t>
+  </si>
+  <si>
+    <t>450.6</t>
+  </si>
+  <si>
+    <t>456.5</t>
+  </si>
+  <si>
+    <t>514.5</t>
+  </si>
+  <si>
+    <t>456.9</t>
+  </si>
+  <si>
+    <t>387.6</t>
+  </si>
+  <si>
+    <t>383.9</t>
+  </si>
+  <si>
+    <t>377.9</t>
+  </si>
+  <si>
+    <t>345.8</t>
+  </si>
+  <si>
+    <t>318.1</t>
+  </si>
+  <si>
+    <t>288.9</t>
+  </si>
+  <si>
+    <t>267.2</t>
+  </si>
+  <si>
+    <t>255.7</t>
+  </si>
+  <si>
+    <t>257.0</t>
+  </si>
+  <si>
+    <t>244.7</t>
+  </si>
+  <si>
+    <t>226.9</t>
+  </si>
+  <si>
+    <t>209.7</t>
+  </si>
+  <si>
+    <t>212.8</t>
+  </si>
+  <si>
+    <t>205.0</t>
+  </si>
+  <si>
+    <t>179.3</t>
+  </si>
+  <si>
+    <t>163.4</t>
+  </si>
+  <si>
+    <t>152.0</t>
+  </si>
+  <si>
+    <t>147.8</t>
+  </si>
+  <si>
+    <t>135.5</t>
+  </si>
+  <si>
+    <t>122.5</t>
+  </si>
+  <si>
+    <t>113.5</t>
+  </si>
+  <si>
+    <t>94.2</t>
+  </si>
+  <si>
+    <t>84.9</t>
+  </si>
+  <si>
+    <t>88.3</t>
+  </si>
+  <si>
+    <t>82.4</t>
+  </si>
+  <si>
+    <t>72.1</t>
+  </si>
+  <si>
+    <t>60.5</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>38.4</t>
+  </si>
+  <si>
+    <t>33.2</t>
+  </si>
+  <si>
+    <t>계</t>
+  </si>
+  <si>
+    <t>2,556.9</t>
+  </si>
+  <si>
+    <t>2,408.7</t>
+  </si>
+  <si>
+    <t>2,323.8</t>
+  </si>
+  <si>
+    <t>2,221.9</t>
+  </si>
+  <si>
+    <t>2,058.5</t>
+  </si>
+  <si>
+    <t>2,040.6</t>
+  </si>
+  <si>
+    <t>2,007.0</t>
+  </si>
+  <si>
+    <t>1,934.2</t>
+  </si>
+  <si>
+    <t>1,833.0</t>
+  </si>
+  <si>
+    <t>1,740.8</t>
+  </si>
+  <si>
+    <t>1,638.5</t>
+  </si>
+  <si>
+    <t>1,570.9</t>
+  </si>
+  <si>
+    <t>1,504.7</t>
+  </si>
+  <si>
+    <t>1,448.6</t>
+  </si>
+  <si>
+    <t>1,379.5</t>
+  </si>
+  <si>
+    <t>1,255.3</t>
+  </si>
+  <si>
+    <t>1,203.0</t>
+  </si>
+  <si>
+    <t>1,134.5</t>
+  </si>
+  <si>
+    <t>1,045.7</t>
+  </si>
+  <si>
+    <t>995.2</t>
+  </si>
+  <si>
+    <t>942.9</t>
+  </si>
+  <si>
+    <t>868.1</t>
+  </si>
+  <si>
+    <t>813.2</t>
+  </si>
+  <si>
+    <t>732.7</t>
+  </si>
+  <si>
+    <t>675.7</t>
+  </si>
+  <si>
+    <t>613.1</t>
+  </si>
+  <si>
+    <t>556.8</t>
+  </si>
+  <si>
+    <t>560.5</t>
+  </si>
+  <si>
+    <t>507.8</t>
+  </si>
+  <si>
+    <t>452.2</t>
+  </si>
+  <si>
+    <t>385.0</t>
+  </si>
+  <si>
+    <t>325.6</t>
+  </si>
+  <si>
+    <t>286.4</t>
+  </si>
+  <si>
+    <t>250.0</t>
+  </si>
+  <si>
+    <t>206.7</t>
+  </si>
+  <si>
+    <t>경상GDP</t>
+  </si>
+  <si>
+    <t>2024 p)</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>조원</t>
+  </si>
+  <si>
+    <t>단위:</t>
+  </si>
+  <si>
+    <t>조세부담률</t>
+  </si>
+  <si>
+    <t>통계표명:</t>
+  </si>
+  <si>
+    <t>https://www.index.go.kr/unity/potal/main/EachDtlPageDetail.do?idx_cd=1122</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lofin365.go.kr/portal/LF6100000.do?ntcaClsDvCd=FSL406&amp;dtsSnum=655418&amp;curPage=1</t>
+  </si>
+  <si>
+    <t>https://www.data.go.kr/data/15038802/fileData.do?recommendDataYn=Y#</t>
   </si>
 </sst>
 </file>
@@ -530,7 +1493,7 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,8 +1517,23 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -568,8 +1546,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -577,16 +1566,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -600,18 +1607,49 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -624,6 +1662,2278 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-2B03-40C0-89EA-7B15557B0A54}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2B03-40C0-89EA-7B15557B0A54}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2B03-40C0-89EA-7B15557B0A54}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{CC91ED26-C3E2-44FA-8E43-C3E5D3023EF4}" type="CATEGORYNAME">
+                      <a:rPr lang="ko-KR" altLang="en-US">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr/>
+                      <a:t>[범주 이름]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{7E9329CC-9D5C-4F02-A06D-91D4B36056FA}" type="VALUE">
+                      <a:rPr lang="en-US" altLang="ko-KR" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr/>
+                      <a:t>[값]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" altLang="ko-KR" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-2B03-40C0-89EA-7B15557B0A54}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D88F98B1-73F0-497B-9BB0-D8F927A69267}" type="CATEGORYNAME">
+                      <a:rPr lang="ko-KR" altLang="en-US">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr/>
+                      <a:t>[범주 이름]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{0D46DEBA-3899-4DBF-B15F-9FDD371F5F15}" type="VALUE">
+                      <a:rPr lang="en-US" altLang="ko-KR" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr/>
+                      <a:t>[값]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" altLang="ko-KR" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-2B03-40C0-89EA-7B15557B0A54}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.9531935117327474E-2"/>
+                  <c:y val="-3.985549299085353E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-2B03-40C0-89EA-7B15557B0A54}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'기능별 세출실적'!$A$26:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>교육</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>일반·지방행정</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>사회복지</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>국방</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>교통및물류</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>기타</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'기능별 세출실적'!$B$26:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.300000000000011</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2B03-40C0-89EA-7B15557B0A54}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1050"/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2DF0-4C54-8C7B-365647726614}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2DF0-4C54-8C7B-365647726614}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2DF0-4C54-8C7B-365647726614}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2DF0-4C54-8C7B-365647726614}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-2DF0-4C54-8C7B-365647726614}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-2DF0-4C54-8C7B-365647726614}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                    <a:spAutoFit/>
+                  </a:bodyPr>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:fld id="{BFCAD7AC-CA8F-4C15-863C-02C0D4A80463}" type="CATEGORYNAME">
+                      <a:rPr lang="ko-KR" altLang="en-US">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr>
+                        <a:defRPr sz="1050">
+                          <a:solidFill>
+                            <a:schemeClr val="bg1"/>
+                          </a:solidFill>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:t>[범주 이름]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{69A968D7-4A08-47C2-93A9-F2CC394940B3}" type="VALUE">
+                      <a:rPr lang="en-US" altLang="ko-KR" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:pPr>
+                        <a:defRPr sz="1050">
+                          <a:solidFill>
+                            <a:schemeClr val="bg1"/>
+                          </a:solidFill>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:t>[값]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" altLang="ko-KR" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-2DF0-4C54-8C7B-365647726614}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.16561953193350831"/>
+                  <c:y val="6.2503318724882254E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ko-KR"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-2DF0-4C54-8C7B-365647726614}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'성질별 분류'!$A$39:$A$44</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>이전지출</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>전출금</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>인건비</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>자산취득</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>물건비</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>기타</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'성질별 분류'!$B$39:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>57.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0999999999999943</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-2DF0-4C54-8C7B-365647726614}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>627984</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>570834</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="차트 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFD39D08-2933-FDFA-336D-8162819109F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28260DAC-A6E8-4C10-89D9-69A0E4E9A637}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>172908</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>329399</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1" descr="텍스트, 스크린샷, 라인, 평행이(가) 표시된 사진&#10;&#10;AI 생성 콘텐츠는 정확하지 않을 수 있습니다.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BE44877-4AB4-4AD8-3612-E58BC771FC99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="1487358"/>
+          <a:ext cx="4701374" cy="3922842"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="43p 그림2-3"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>기능별 분류</v>
+          </cell>
+          <cell r="C5">
+            <v>20.7</v>
+          </cell>
+          <cell r="D5">
+            <v>5.5</v>
+          </cell>
+          <cell r="E5">
+            <v>14.1</v>
+          </cell>
+          <cell r="F5">
+            <v>20.3</v>
+          </cell>
+          <cell r="G5">
+            <v>17.5</v>
+          </cell>
+          <cell r="H5">
+            <v>5</v>
+          </cell>
+          <cell r="I5">
+            <v>16.899999999999999</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24" t="str">
+            <v>한국</v>
+          </cell>
+          <cell r="G24">
+            <v>35.159999999999997</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25" t="str">
+            <v>미국</v>
+          </cell>
+          <cell r="G25">
+            <v>39.130000000000003</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26" t="str">
+            <v>일본</v>
+          </cell>
+          <cell r="G26">
+            <v>40.6</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27" t="str">
+            <v>포르투갈</v>
+          </cell>
+          <cell r="G27">
+            <v>42.31</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28" t="str">
+            <v>영국</v>
+          </cell>
+          <cell r="G28">
+            <v>47.13</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29" t="str">
+            <v>독일</v>
+          </cell>
+          <cell r="G29">
+            <v>48.38</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30" t="str">
+            <v>스웨덴</v>
+          </cell>
+          <cell r="G30">
+            <v>49.36</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31" t="str">
+            <v>이탈리아</v>
+          </cell>
+          <cell r="G31">
+            <v>53.95</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32" t="str">
+            <v>프랑스</v>
+          </cell>
+          <cell r="G32">
+            <v>56.95</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1050,7 +4360,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>125</v>
       </c>
       <c r="B5" t="s">
@@ -1094,7 +4404,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>127</v>
       </c>
       <c r="B6" t="s">
@@ -1138,7 +4448,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B7" t="s">
@@ -1182,7 +4492,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B8" t="s">
@@ -1226,7 +4536,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>133</v>
       </c>
       <c r="B9" t="s">
@@ -1270,7 +4580,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>135</v>
       </c>
       <c r="B10" t="s">
@@ -1314,7 +4624,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B11" t="s">
@@ -1358,7 +4668,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B12" t="s">
@@ -1418,7 +4728,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B15" t="s">
@@ -1462,7 +4772,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>143</v>
       </c>
       <c r="B16" t="s">
@@ -1543,7 +4853,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>145</v>
       </c>
       <c r="B24" t="s">
@@ -1591,7 +4901,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A25" s="4"/>
+      <c r="A25" s="6"/>
       <c r="B25" t="s">
         <v>147</v>
       </c>
@@ -1637,10 +4947,10 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B26" s="4"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="1">
         <f t="shared" ref="C26:L27" si="2">E8/1000000</f>
         <v>88.042483000000004</v>
@@ -1683,10 +4993,10 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="4"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="1">
         <f t="shared" si="2"/>
         <v>0.190085</v>
@@ -1729,10 +5039,10 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B28" s="4"/>
+      <c r="B28" s="6"/>
       <c r="C28" s="1">
         <f>SUM(C24:C27)</f>
         <v>339.35101700000001</v>
@@ -1775,16 +5085,16 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="4"/>
+      <c r="B29" s="6"/>
       <c r="C29" s="3">
         <f>(E4*1000000)/(E13*100000000)</f>
         <v>0.20467240149759316</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" ref="C29:L29" si="4">(F4*1000000)/(F13*100000000)</f>
+        <f t="shared" ref="D29:L29" si="4">(F4*1000000)/(F13*100000000)</f>
         <v>0.20356026690570134</v>
       </c>
       <c r="E29" s="3">
@@ -1828,6 +5138,27 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C619157F-6CEC-482D-AF41-21C277C80601}">
+  <dimension ref="A3:A4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4434,4 +7765,4284 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7200B0-C6B5-4E5B-B524-74E0C847E9B4}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="23.08203125" customWidth="1"/>
+    <col min="2" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I5" t="s">
+        <v>179</v>
+      </c>
+      <c r="K5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>553997680</v>
+      </c>
+      <c r="C6">
+        <v>529462952</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>490414468</v>
+      </c>
+      <c r="F6">
+        <v>24534729</v>
+      </c>
+      <c r="G6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H6">
+        <v>39048484</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7">
+        <v>104266587</v>
+      </c>
+      <c r="C7">
+        <v>101632562</v>
+      </c>
+      <c r="D7">
+        <v>19.2</v>
+      </c>
+      <c r="E7">
+        <v>88244442</v>
+      </c>
+      <c r="F7">
+        <v>2634025</v>
+      </c>
+      <c r="G7">
+        <v>2.5</v>
+      </c>
+      <c r="H7">
+        <v>13388120</v>
+      </c>
+      <c r="I7">
+        <v>15.2</v>
+      </c>
+      <c r="K7">
+        <f>RANK(C7,$C$7:$C$22)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8">
+        <v>24136885</v>
+      </c>
+      <c r="C8">
+        <v>23762215</v>
+      </c>
+      <c r="D8">
+        <v>4.5</v>
+      </c>
+      <c r="E8">
+        <v>22170510</v>
+      </c>
+      <c r="F8">
+        <v>374670</v>
+      </c>
+      <c r="G8">
+        <v>1.6</v>
+      </c>
+      <c r="H8">
+        <v>1591706</v>
+      </c>
+      <c r="I8">
+        <v>7.2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" ref="K8:K22" si="0">RANK(C8,$C$7:$C$22)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9">
+        <v>4523968</v>
+      </c>
+      <c r="C9">
+        <v>4344570</v>
+      </c>
+      <c r="D9">
+        <v>0.8</v>
+      </c>
+      <c r="E9">
+        <v>3494193</v>
+      </c>
+      <c r="F9">
+        <v>179398</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>850377</v>
+      </c>
+      <c r="I9">
+        <v>24.3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10">
+        <v>62383283</v>
+      </c>
+      <c r="C10">
+        <v>60035756</v>
+      </c>
+      <c r="D10">
+        <v>11.3</v>
+      </c>
+      <c r="E10">
+        <v>57637727</v>
+      </c>
+      <c r="F10">
+        <v>2347527</v>
+      </c>
+      <c r="G10">
+        <v>3.8</v>
+      </c>
+      <c r="H10">
+        <v>2398029</v>
+      </c>
+      <c r="I10">
+        <v>4.2</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11">
+        <v>109982241</v>
+      </c>
+      <c r="C11">
+        <v>105275933</v>
+      </c>
+      <c r="D11">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E11">
+        <v>99436880</v>
+      </c>
+      <c r="F11">
+        <v>4706308</v>
+      </c>
+      <c r="G11">
+        <v>4.3</v>
+      </c>
+      <c r="H11">
+        <v>5839053</v>
+      </c>
+      <c r="I11">
+        <v>5.9</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12">
+        <v>5234085</v>
+      </c>
+      <c r="C12">
+        <v>4960532</v>
+      </c>
+      <c r="D12">
+        <v>0.9</v>
+      </c>
+      <c r="E12">
+        <v>4859367</v>
+      </c>
+      <c r="F12">
+        <v>273552</v>
+      </c>
+      <c r="G12">
+        <v>5.2</v>
+      </c>
+      <c r="H12">
+        <v>101166</v>
+      </c>
+      <c r="I12">
+        <v>2.1</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13">
+        <v>18138941</v>
+      </c>
+      <c r="C13">
+        <v>16288580</v>
+      </c>
+      <c r="D13">
+        <v>3.1</v>
+      </c>
+      <c r="E13">
+        <v>15941175</v>
+      </c>
+      <c r="F13">
+        <v>1850360</v>
+      </c>
+      <c r="G13">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="H13">
+        <v>347405</v>
+      </c>
+      <c r="I13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14">
+        <v>85956604</v>
+      </c>
+      <c r="C14">
+        <v>84533985</v>
+      </c>
+      <c r="D14">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>77853242</v>
+      </c>
+      <c r="F14">
+        <v>1422619</v>
+      </c>
+      <c r="G14">
+        <v>1.7</v>
+      </c>
+      <c r="H14">
+        <v>6680743</v>
+      </c>
+      <c r="I14">
+        <v>8.6</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15">
+        <v>16383421</v>
+      </c>
+      <c r="C15">
+        <v>16266748</v>
+      </c>
+      <c r="D15">
+        <v>3.1</v>
+      </c>
+      <c r="E15">
+        <v>17228625</v>
+      </c>
+      <c r="F15">
+        <v>116673</v>
+      </c>
+      <c r="G15">
+        <v>0.7</v>
+      </c>
+      <c r="H15">
+        <v>-961877</v>
+      </c>
+      <c r="I15">
+        <v>-5.6</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16">
+        <v>30223068</v>
+      </c>
+      <c r="C16">
+        <v>27612406</v>
+      </c>
+      <c r="D16">
+        <v>5.2</v>
+      </c>
+      <c r="E16">
+        <v>27916009</v>
+      </c>
+      <c r="F16">
+        <v>2610662</v>
+      </c>
+      <c r="G16">
+        <v>8.6</v>
+      </c>
+      <c r="H16">
+        <v>-303604</v>
+      </c>
+      <c r="I16">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17">
+        <v>18845738</v>
+      </c>
+      <c r="C17">
+        <v>18397688</v>
+      </c>
+      <c r="D17">
+        <v>3.5</v>
+      </c>
+      <c r="E17">
+        <v>17601721</v>
+      </c>
+      <c r="F17">
+        <v>448049</v>
+      </c>
+      <c r="G17">
+        <v>2.4</v>
+      </c>
+      <c r="H17">
+        <v>795968</v>
+      </c>
+      <c r="I17">
+        <v>4.5</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18">
+        <v>36440803</v>
+      </c>
+      <c r="C18">
+        <v>33542973</v>
+      </c>
+      <c r="D18">
+        <v>6.3</v>
+      </c>
+      <c r="E18">
+        <v>27872563</v>
+      </c>
+      <c r="F18">
+        <v>2897830</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>5670410</v>
+      </c>
+      <c r="I18">
+        <v>20.3</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19">
+        <v>13742799</v>
+      </c>
+      <c r="C19">
+        <v>12458484</v>
+      </c>
+      <c r="D19">
+        <v>2.4</v>
+      </c>
+      <c r="E19">
+        <v>11347457</v>
+      </c>
+      <c r="F19">
+        <v>1284315</v>
+      </c>
+      <c r="G19">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H19">
+        <v>1111027</v>
+      </c>
+      <c r="I19">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20">
+        <v>11564550</v>
+      </c>
+      <c r="C20">
+        <v>10835351</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>8941822</v>
+      </c>
+      <c r="F20">
+        <v>729200</v>
+      </c>
+      <c r="G20">
+        <v>6.3</v>
+      </c>
+      <c r="H20">
+        <v>1893529</v>
+      </c>
+      <c r="I20">
+        <v>21.2</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21">
+        <v>8990880</v>
+      </c>
+      <c r="C21">
+        <v>8876869</v>
+      </c>
+      <c r="D21">
+        <v>1.7</v>
+      </c>
+      <c r="E21">
+        <v>9261537</v>
+      </c>
+      <c r="F21">
+        <v>114011</v>
+      </c>
+      <c r="G21">
+        <v>1.3</v>
+      </c>
+      <c r="H21">
+        <v>-384668</v>
+      </c>
+      <c r="I21">
+        <v>-4.2</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22">
+        <v>3183828</v>
+      </c>
+      <c r="C22">
+        <v>638300</v>
+      </c>
+      <c r="D22">
+        <v>0.1</v>
+      </c>
+      <c r="E22">
+        <v>607200</v>
+      </c>
+      <c r="F22">
+        <v>2545528</v>
+      </c>
+      <c r="G22">
+        <v>80</v>
+      </c>
+      <c r="H22">
+        <v>31100</v>
+      </c>
+      <c r="I22">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A26" t="str">
+        <f>A11</f>
+        <v>교육</v>
+      </c>
+      <c r="B26">
+        <f>D11</f>
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A27" t="str">
+        <f>A7</f>
+        <v>일반·지방행정</v>
+      </c>
+      <c r="B27">
+        <f>D7</f>
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A28" t="str">
+        <f>A14</f>
+        <v>사회복지</v>
+      </c>
+      <c r="B28">
+        <f>D14</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A29" t="str">
+        <f>A10</f>
+        <v>국방</v>
+      </c>
+      <c r="B29">
+        <f>D10</f>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A30" t="str">
+        <f>A18</f>
+        <v>교통및물류</v>
+      </c>
+      <c r="B30">
+        <f>D18</f>
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B31">
+        <f>100-SUM(B26:B30)</f>
+        <v>27.300000000000011</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61589BF4-E830-42F7-B86B-5B9A064320EC}">
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" t="s">
+        <v>217</v>
+      </c>
+      <c r="K5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>553997680</v>
+      </c>
+      <c r="C6">
+        <v>529462952</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>490414468</v>
+      </c>
+      <c r="F6">
+        <v>24534729</v>
+      </c>
+      <c r="G6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H6">
+        <v>39048484</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7">
+        <v>47508735</v>
+      </c>
+      <c r="C7">
+        <v>46867061</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="E7">
+        <v>44810387</v>
+      </c>
+      <c r="F7">
+        <v>641674</v>
+      </c>
+      <c r="G7">
+        <v>1.4</v>
+      </c>
+      <c r="H7">
+        <v>2056675</v>
+      </c>
+      <c r="I7">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8">
+        <v>30571939</v>
+      </c>
+      <c r="C8">
+        <v>29487082</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="E8">
+        <v>29688699</v>
+      </c>
+      <c r="F8">
+        <v>1084857</v>
+      </c>
+      <c r="G8">
+        <v>3.5</v>
+      </c>
+      <c r="H8">
+        <v>-201617</v>
+      </c>
+      <c r="I8">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9">
+        <v>24768329</v>
+      </c>
+      <c r="C9">
+        <v>24067549</v>
+      </c>
+      <c r="D9">
+        <v>4.5</v>
+      </c>
+      <c r="E9">
+        <v>24143828</v>
+      </c>
+      <c r="F9">
+        <v>700780</v>
+      </c>
+      <c r="G9">
+        <v>2.8</v>
+      </c>
+      <c r="H9">
+        <v>-76279</v>
+      </c>
+      <c r="I9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10">
+        <v>712495</v>
+      </c>
+      <c r="C10">
+        <v>669753</v>
+      </c>
+      <c r="D10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E10">
+        <v>656138</v>
+      </c>
+      <c r="F10">
+        <v>42742</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>13615</v>
+      </c>
+      <c r="I10">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11">
+        <v>123266</v>
+      </c>
+      <c r="C11">
+        <v>119496</v>
+      </c>
+      <c r="D11">
+        <v>0.4</v>
+      </c>
+      <c r="E11">
+        <v>129558</v>
+      </c>
+      <c r="F11">
+        <v>3771</v>
+      </c>
+      <c r="G11">
+        <v>3.1</v>
+      </c>
+      <c r="H11">
+        <v>-10063</v>
+      </c>
+      <c r="I11">
+        <v>-7.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12">
+        <v>182195</v>
+      </c>
+      <c r="C12">
+        <v>175306</v>
+      </c>
+      <c r="D12">
+        <v>0.6</v>
+      </c>
+      <c r="E12">
+        <v>172059</v>
+      </c>
+      <c r="F12">
+        <v>6889</v>
+      </c>
+      <c r="G12">
+        <v>3.8</v>
+      </c>
+      <c r="H12">
+        <v>3247</v>
+      </c>
+      <c r="I12">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13">
+        <v>1064534</v>
+      </c>
+      <c r="C13">
+        <v>1049580</v>
+      </c>
+      <c r="D13">
+        <v>3.6</v>
+      </c>
+      <c r="E13">
+        <v>1039090</v>
+      </c>
+      <c r="F13">
+        <v>14954</v>
+      </c>
+      <c r="G13">
+        <v>1.4</v>
+      </c>
+      <c r="H13">
+        <v>10490</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14">
+        <v>2677357</v>
+      </c>
+      <c r="C14">
+        <v>2450432</v>
+      </c>
+      <c r="D14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E14">
+        <v>2640074</v>
+      </c>
+      <c r="F14">
+        <v>226925</v>
+      </c>
+      <c r="G14">
+        <v>8.5</v>
+      </c>
+      <c r="H14">
+        <v>-189642</v>
+      </c>
+      <c r="I14">
+        <v>-7.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15">
+        <v>892100</v>
+      </c>
+      <c r="C15">
+        <v>824491</v>
+      </c>
+      <c r="D15">
+        <v>2.8</v>
+      </c>
+      <c r="E15">
+        <v>804591</v>
+      </c>
+      <c r="F15">
+        <v>67609</v>
+      </c>
+      <c r="G15">
+        <v>7.6</v>
+      </c>
+      <c r="H15">
+        <v>19900</v>
+      </c>
+      <c r="I15">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16">
+        <v>151662</v>
+      </c>
+      <c r="C16">
+        <v>130474</v>
+      </c>
+      <c r="D16">
+        <v>0.4</v>
+      </c>
+      <c r="E16">
+        <v>103360</v>
+      </c>
+      <c r="F16">
+        <v>21188</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>27114</v>
+      </c>
+      <c r="I16">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17">
+        <v>318045703</v>
+      </c>
+      <c r="C17">
+        <v>306528786</v>
+      </c>
+      <c r="D17" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="E17">
+        <v>301866968</v>
+      </c>
+      <c r="F17">
+        <v>11516917</v>
+      </c>
+      <c r="G17">
+        <v>3.6</v>
+      </c>
+      <c r="H17">
+        <v>4661818</v>
+      </c>
+      <c r="I17">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18">
+        <v>26396045</v>
+      </c>
+      <c r="C18">
+        <v>26005827</v>
+      </c>
+      <c r="D18">
+        <v>8.5</v>
+      </c>
+      <c r="E18">
+        <v>24186363</v>
+      </c>
+      <c r="F18">
+        <v>390217</v>
+      </c>
+      <c r="G18">
+        <v>1.5</v>
+      </c>
+      <c r="H18">
+        <v>1819464</v>
+      </c>
+      <c r="I18">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19">
+        <v>21640590</v>
+      </c>
+      <c r="C19">
+        <v>20639354</v>
+      </c>
+      <c r="D19">
+        <v>6.7</v>
+      </c>
+      <c r="E19">
+        <v>19978134</v>
+      </c>
+      <c r="F19">
+        <v>1001236</v>
+      </c>
+      <c r="G19">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H19">
+        <v>661219</v>
+      </c>
+      <c r="I19">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20">
+        <v>220555006</v>
+      </c>
+      <c r="C20">
+        <v>211316428</v>
+      </c>
+      <c r="D20">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="E20">
+        <v>209325393</v>
+      </c>
+      <c r="F20">
+        <v>9238578</v>
+      </c>
+      <c r="G20">
+        <v>4.2</v>
+      </c>
+      <c r="H20">
+        <v>1991035</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21">
+        <v>2484601</v>
+      </c>
+      <c r="C21">
+        <v>2452546</v>
+      </c>
+      <c r="D21">
+        <v>0.8</v>
+      </c>
+      <c r="E21">
+        <v>1938064</v>
+      </c>
+      <c r="F21">
+        <v>32056</v>
+      </c>
+      <c r="G21">
+        <v>1.3</v>
+      </c>
+      <c r="H21">
+        <v>514482</v>
+      </c>
+      <c r="I21">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22">
+        <v>24560354</v>
+      </c>
+      <c r="C22">
+        <v>23839682</v>
+      </c>
+      <c r="D22">
+        <v>7.8</v>
+      </c>
+      <c r="E22">
+        <v>19026429</v>
+      </c>
+      <c r="F22">
+        <v>720671</v>
+      </c>
+      <c r="G22">
+        <v>2.9</v>
+      </c>
+      <c r="H22">
+        <v>4813254</v>
+      </c>
+      <c r="I22">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23">
+        <v>22409107</v>
+      </c>
+      <c r="C23">
+        <v>22274949</v>
+      </c>
+      <c r="D23">
+        <v>7.3</v>
+      </c>
+      <c r="E23">
+        <v>27412585</v>
+      </c>
+      <c r="F23">
+        <v>134158</v>
+      </c>
+      <c r="G23">
+        <v>0.6</v>
+      </c>
+      <c r="H23">
+        <v>-5137636</v>
+      </c>
+      <c r="I23">
+        <v>-18.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24">
+        <v>43796475</v>
+      </c>
+      <c r="C24">
+        <v>39706277</v>
+      </c>
+      <c r="D24" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="E24">
+        <v>36890836</v>
+      </c>
+      <c r="F24">
+        <v>4090198</v>
+      </c>
+      <c r="G24">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H24">
+        <v>2815441</v>
+      </c>
+      <c r="I24">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25">
+        <v>2489373</v>
+      </c>
+      <c r="C25">
+        <v>2347421</v>
+      </c>
+      <c r="D25">
+        <v>5.9</v>
+      </c>
+      <c r="E25">
+        <v>2079879</v>
+      </c>
+      <c r="F25">
+        <v>141952</v>
+      </c>
+      <c r="G25">
+        <v>5.7</v>
+      </c>
+      <c r="H25">
+        <v>267541</v>
+      </c>
+      <c r="I25">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26">
+        <v>16947235</v>
+      </c>
+      <c r="C26">
+        <v>14396006</v>
+      </c>
+      <c r="D26">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="E26">
+        <v>13679163</v>
+      </c>
+      <c r="F26">
+        <v>2551229</v>
+      </c>
+      <c r="G26">
+        <v>15.1</v>
+      </c>
+      <c r="H26">
+        <v>716843</v>
+      </c>
+      <c r="I26">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27">
+        <v>16333238</v>
+      </c>
+      <c r="C27">
+        <v>15608052</v>
+      </c>
+      <c r="D27">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E27">
+        <v>14844128</v>
+      </c>
+      <c r="F27">
+        <v>725185</v>
+      </c>
+      <c r="G27">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H27">
+        <v>763924</v>
+      </c>
+      <c r="I27">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A28" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28">
+        <v>46636</v>
+      </c>
+      <c r="C28">
+        <v>41934</v>
+      </c>
+      <c r="D28">
+        <v>0.1</v>
+      </c>
+      <c r="E28">
+        <v>34853</v>
+      </c>
+      <c r="F28">
+        <v>4702</v>
+      </c>
+      <c r="G28">
+        <v>10.1</v>
+      </c>
+      <c r="H28">
+        <v>7081</v>
+      </c>
+      <c r="I28">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A29" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29">
+        <v>686893</v>
+      </c>
+      <c r="C29">
+        <v>685287</v>
+      </c>
+      <c r="D29">
+        <v>1.7</v>
+      </c>
+      <c r="E29">
+        <v>737859</v>
+      </c>
+      <c r="F29">
+        <v>1606</v>
+      </c>
+      <c r="G29">
+        <v>0.2</v>
+      </c>
+      <c r="H29">
+        <v>-52572</v>
+      </c>
+      <c r="I29">
+        <v>-7.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30">
+        <v>4010704</v>
+      </c>
+      <c r="C30">
+        <v>3938204</v>
+      </c>
+      <c r="D30">
+        <v>9.9</v>
+      </c>
+      <c r="E30">
+        <v>3086393</v>
+      </c>
+      <c r="F30">
+        <v>72500</v>
+      </c>
+      <c r="G30">
+        <v>1.8</v>
+      </c>
+      <c r="H30">
+        <v>851811</v>
+      </c>
+      <c r="I30">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A31" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B31">
+        <v>3255055</v>
+      </c>
+      <c r="C31">
+        <v>2662031</v>
+      </c>
+      <c r="D31">
+        <v>6.7</v>
+      </c>
+      <c r="E31">
+        <v>2407275</v>
+      </c>
+      <c r="F31">
+        <v>593024</v>
+      </c>
+      <c r="G31">
+        <v>18.2</v>
+      </c>
+      <c r="H31">
+        <v>254756</v>
+      </c>
+      <c r="I31">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A32" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32">
+        <v>27341</v>
+      </c>
+      <c r="C32">
+        <v>27341</v>
+      </c>
+      <c r="D32">
+        <v>0.1</v>
+      </c>
+      <c r="E32">
+        <v>21285</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>6056</v>
+      </c>
+      <c r="I32">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33">
+        <v>21929819</v>
+      </c>
+      <c r="C33">
+        <v>21573629</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E33">
+        <v>8363387</v>
+      </c>
+      <c r="F33">
+        <v>356190</v>
+      </c>
+      <c r="G33">
+        <v>1.6</v>
+      </c>
+      <c r="H33">
+        <v>13210242</v>
+      </c>
+      <c r="I33">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34">
+        <v>88930779</v>
+      </c>
+      <c r="C34">
+        <v>84635446</v>
+      </c>
+      <c r="D34" s="2">
+        <v>16</v>
+      </c>
+      <c r="E34">
+        <v>68161058</v>
+      </c>
+      <c r="F34">
+        <v>4295334</v>
+      </c>
+      <c r="G34">
+        <v>4.8</v>
+      </c>
+      <c r="H34">
+        <v>16474387</v>
+      </c>
+      <c r="I34">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35">
+        <v>3214230</v>
+      </c>
+      <c r="C35">
+        <v>664671</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E35">
+        <v>633133</v>
+      </c>
+      <c r="F35">
+        <v>2549559</v>
+      </c>
+      <c r="G35">
+        <v>79.3</v>
+      </c>
+      <c r="H35">
+        <v>31538</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" t="str">
+        <f>A17</f>
+        <v>이전지출</v>
+      </c>
+      <c r="B39">
+        <f>D17</f>
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" t="str">
+        <f>A34</f>
+        <v>전출금</v>
+      </c>
+      <c r="B40">
+        <f>D34</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" t="str">
+        <f>A7</f>
+        <v>인건비</v>
+      </c>
+      <c r="B41">
+        <f>D7</f>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" t="str">
+        <f>A24</f>
+        <v>자산취득</v>
+      </c>
+      <c r="B42">
+        <f>D24</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" t="str">
+        <f>A8</f>
+        <v>물건비</v>
+      </c>
+      <c r="B43">
+        <f>D8</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>183</v>
+      </c>
+      <c r="B44">
+        <f>100-SUM(B39:B43)</f>
+        <v>4.0999999999999943</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EC110D-8FF3-4B66-BBA3-D07A1ABC65F4}">
+  <dimension ref="A14:E24"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16">
+        <v>56.95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="1">
+        <f>B22</f>
+        <v>35.159999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17">
+        <v>53.95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E17" s="1">
+        <f>B23</f>
+        <v>39.130000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18">
+        <v>42.31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" s="1">
+        <f>B24</f>
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19">
+        <v>47.13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="1">
+        <f>B18</f>
+        <v>42.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20">
+        <v>49.36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="1">
+        <f>B19</f>
+        <v>47.13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21">
+        <v>48.38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E21" s="1">
+        <f>B21</f>
+        <v>48.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B22">
+        <v>35.159999999999997</v>
+      </c>
+      <c r="D22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" s="1">
+        <f>B20</f>
+        <v>49.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23">
+        <v>39.130000000000003</v>
+      </c>
+      <c r="D23" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="1">
+        <f>B17</f>
+        <v>53.95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24">
+        <v>40.6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="1">
+        <f>B16</f>
+        <v>56.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C82C6841-B742-47C2-8779-C1219F9E2C3E}">
+  <dimension ref="A5:A6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{06B84879-0F06-4BD9-B977-B1EA3F00CFA7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73866090-CD41-4F5B-B196-7D339DA5988C}">
+  <dimension ref="A2:AA30"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>2018</v>
+      </c>
+      <c r="C2">
+        <v>2019</v>
+      </c>
+      <c r="D2">
+        <v>2020</v>
+      </c>
+      <c r="E2">
+        <v>2021</v>
+      </c>
+      <c r="F2">
+        <v>2022</v>
+      </c>
+      <c r="G2">
+        <v>2023</v>
+      </c>
+      <c r="H2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3">
+        <v>316218484</v>
+      </c>
+      <c r="C3">
+        <v>332239672</v>
+      </c>
+      <c r="D3">
+        <v>392367040</v>
+      </c>
+      <c r="E3">
+        <v>438363287</v>
+      </c>
+      <c r="F3">
+        <v>493867232</v>
+      </c>
+      <c r="G3">
+        <v>407928318</v>
+      </c>
+      <c r="H3">
+        <v>437317819</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4">
+        <v>285891988</v>
+      </c>
+      <c r="C4">
+        <v>286031996</v>
+      </c>
+      <c r="D4">
+        <v>276278187</v>
+      </c>
+      <c r="E4">
+        <v>332504797</v>
+      </c>
+      <c r="F4">
+        <v>385159576</v>
+      </c>
+      <c r="G4">
+        <v>333939610</v>
+      </c>
+      <c r="H4">
+        <v>326179303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5">
+        <v>254770202</v>
+      </c>
+      <c r="C5">
+        <v>255804538</v>
+      </c>
+      <c r="D5">
+        <v>246987193</v>
+      </c>
+      <c r="E5">
+        <v>296445033</v>
+      </c>
+      <c r="F5">
+        <v>352274995</v>
+      </c>
+      <c r="G5">
+        <v>306059472</v>
+      </c>
+      <c r="H5">
+        <v>298259369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6">
+        <v>8815210</v>
+      </c>
+      <c r="C6">
+        <v>7882126</v>
+      </c>
+      <c r="D6">
+        <v>7058540</v>
+      </c>
+      <c r="E6">
+        <v>8227000</v>
+      </c>
+      <c r="F6">
+        <v>10324118</v>
+      </c>
+      <c r="G6">
+        <v>7288282</v>
+      </c>
+      <c r="H6">
+        <v>6972267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7">
+        <v>269</v>
+      </c>
+      <c r="C7">
+        <v>271</v>
+      </c>
+      <c r="D7">
+        <v>178</v>
+      </c>
+      <c r="E7">
+        <v>287</v>
+      </c>
+      <c r="F7">
+        <v>898</v>
+      </c>
+      <c r="G7">
+        <v>137</v>
+      </c>
+      <c r="H7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8">
+        <v>15334854</v>
+      </c>
+      <c r="C8">
+        <v>14562707</v>
+      </c>
+      <c r="D8">
+        <v>13937883</v>
+      </c>
+      <c r="E8">
+        <v>16598390</v>
+      </c>
+      <c r="F8">
+        <v>11116375</v>
+      </c>
+      <c r="G8">
+        <v>10843590</v>
+      </c>
+      <c r="H8">
+        <v>11389082</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9">
+        <v>5098691</v>
+      </c>
+      <c r="C9">
+        <v>5111088</v>
+      </c>
+      <c r="D9">
+        <v>4693743</v>
+      </c>
+      <c r="E9">
+        <v>5103866</v>
+      </c>
+      <c r="F9">
+        <v>4644380</v>
+      </c>
+      <c r="G9">
+        <v>5151619</v>
+      </c>
+      <c r="H9">
+        <v>5373797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10">
+        <v>1872762</v>
+      </c>
+      <c r="C10">
+        <v>2671265</v>
+      </c>
+      <c r="D10">
+        <v>3600650</v>
+      </c>
+      <c r="E10">
+        <v>6130222</v>
+      </c>
+      <c r="F10">
+        <v>6798810</v>
+      </c>
+      <c r="G10">
+        <v>4596509</v>
+      </c>
+      <c r="H10">
+        <v>4184709</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11">
+        <v>30268931</v>
+      </c>
+      <c r="C11">
+        <v>46153681</v>
+      </c>
+      <c r="D11">
+        <v>116088853</v>
+      </c>
+      <c r="E11">
+        <v>105858490</v>
+      </c>
+      <c r="F11">
+        <v>108681334</v>
+      </c>
+      <c r="G11">
+        <v>73988708</v>
+      </c>
+      <c r="H11">
+        <v>111138516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A13" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13">
+        <v>57565</v>
+      </c>
+      <c r="C13">
+        <v>53995</v>
+      </c>
+      <c r="F13">
+        <v>26322</v>
+      </c>
+      <c r="J13">
+        <v>2018</v>
+      </c>
+      <c r="K13">
+        <v>2019</v>
+      </c>
+      <c r="L13">
+        <v>2020</v>
+      </c>
+      <c r="M13">
+        <v>2021</v>
+      </c>
+      <c r="N13">
+        <v>2022</v>
+      </c>
+      <c r="O13">
+        <v>2023</v>
+      </c>
+      <c r="P13">
+        <v>2024</v>
+      </c>
+      <c r="T13">
+        <v>2018</v>
+      </c>
+      <c r="U13">
+        <v>2019</v>
+      </c>
+      <c r="V13">
+        <v>2020</v>
+      </c>
+      <c r="W13">
+        <v>2021</v>
+      </c>
+      <c r="X13">
+        <v>2022</v>
+      </c>
+      <c r="Y13">
+        <v>2023</v>
+      </c>
+      <c r="Z13">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14">
+        <v>299945984</v>
+      </c>
+      <c r="C14">
+        <v>330884136</v>
+      </c>
+      <c r="D14">
+        <v>385222988</v>
+      </c>
+      <c r="E14">
+        <v>417720678</v>
+      </c>
+      <c r="F14">
+        <v>485049157</v>
+      </c>
+      <c r="G14">
+        <v>405886290</v>
+      </c>
+      <c r="H14">
+        <v>435430470</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A15" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15">
+        <v>64132405</v>
+      </c>
+      <c r="C15">
+        <v>70882746</v>
+      </c>
+      <c r="D15">
+        <v>86170021</v>
+      </c>
+      <c r="E15">
+        <v>92407937</v>
+      </c>
+      <c r="F15">
+        <v>103500736</v>
+      </c>
+      <c r="G15">
+        <v>87029976</v>
+      </c>
+      <c r="H15">
+        <v>99140080</v>
+      </c>
+      <c r="J15" s="8">
+        <f>B15/B$14</f>
+        <v>0.21381318110930267</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" ref="K15:P30" si="0">C15/C$14</f>
+        <v>0.21422225573244164</v>
+      </c>
+      <c r="L15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22368867820525809</v>
+      </c>
+      <c r="M15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22121944607204722</v>
+      </c>
+      <c r="N15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21338195213067859</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21441960012987873</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22768291800984897</v>
+      </c>
+      <c r="S15" t="s">
+        <v>247</v>
+      </c>
+      <c r="T15" s="11">
+        <f>SUM(J22)</f>
+        <v>0.16015034226962679</v>
+      </c>
+      <c r="U15" s="11">
+        <f t="shared" ref="U15:AA15" si="1">SUM(K22)</f>
+        <v>0.17125227484463021</v>
+      </c>
+      <c r="V15" s="12">
+        <f t="shared" si="1"/>
+        <v>0.18758528242348818</v>
+      </c>
+      <c r="W15" s="12">
+        <f t="shared" si="1"/>
+        <v>0.17074821467181475</v>
+      </c>
+      <c r="X15" s="12">
+        <f t="shared" si="1"/>
+        <v>0.15606601703670211</v>
+      </c>
+      <c r="Y15" s="12">
+        <f t="shared" si="1"/>
+        <v>0.18580313712985969</v>
+      </c>
+      <c r="Z15" s="12">
+        <f t="shared" si="1"/>
+        <v>0.18883547814189486</v>
+      </c>
+      <c r="AA15" s="11"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A16" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16">
+        <v>17685681</v>
+      </c>
+      <c r="C16">
+        <v>18887154</v>
+      </c>
+      <c r="D16">
+        <v>20081143</v>
+      </c>
+      <c r="E16">
+        <v>20702631</v>
+      </c>
+      <c r="F16">
+        <v>21476477</v>
+      </c>
+      <c r="G16">
+        <v>20989733</v>
+      </c>
+      <c r="H16">
+        <v>22355569</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" ref="J16:J29" si="2">B16/B$14</f>
+        <v>5.8962886464250845E-2</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="0"/>
+        <v>5.7080868935946813E-2</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="0"/>
+        <v>5.2128620631539259E-2</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" si="0"/>
+        <v>4.9560943688787176E-2</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="0"/>
+        <v>4.4276908206233624E-2</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="0"/>
+        <v>5.1713333308203144E-2</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="0"/>
+        <v>5.1341305995421034E-2</v>
+      </c>
+      <c r="S16" t="s">
+        <v>246</v>
+      </c>
+      <c r="T16" s="11">
+        <f>SUM(J18)</f>
+        <v>0.14314324341812157</v>
+      </c>
+      <c r="U16" s="11">
+        <f t="shared" ref="U16:AA16" si="3">SUM(K18)</f>
+        <v>0.14055392187191471</v>
+      </c>
+      <c r="V16" s="12">
+        <f t="shared" si="3"/>
+        <v>0.12488757810060909</v>
+      </c>
+      <c r="W16" s="12">
+        <f t="shared" si="3"/>
+        <v>0.1225281287128429</v>
+      </c>
+      <c r="X16" s="12">
+        <f t="shared" si="3"/>
+        <v>0.10816802017449956</v>
+      </c>
+      <c r="Y16" s="12">
+        <f t="shared" si="3"/>
+        <v>0.13833339381825388</v>
+      </c>
+      <c r="Z16" s="12">
+        <f t="shared" si="3"/>
+        <v>0.13547158975806173</v>
+      </c>
+      <c r="AA16" s="11"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A17" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B17">
+        <v>2487681</v>
+      </c>
+      <c r="C17">
+        <v>2688181</v>
+      </c>
+      <c r="D17">
+        <v>2711778</v>
+      </c>
+      <c r="E17">
+        <v>2935460</v>
+      </c>
+      <c r="F17">
+        <v>3140990</v>
+      </c>
+      <c r="G17">
+        <v>3494193</v>
+      </c>
+      <c r="H17">
+        <v>4344570</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="2"/>
+        <v>8.2937633197315962E-3</v>
+      </c>
+      <c r="K17" s="8">
+        <f t="shared" si="0"/>
+        <v>8.1242365756694964E-3</v>
+      </c>
+      <c r="L17" s="8">
+        <f t="shared" si="0"/>
+        <v>7.0395020143501925E-3</v>
+      </c>
+      <c r="M17" s="8">
+        <f t="shared" si="0"/>
+        <v>7.0273274812600968E-3</v>
+      </c>
+      <c r="N17" s="8">
+        <f t="shared" si="0"/>
+        <v>6.4756117079490154E-3</v>
+      </c>
+      <c r="O17" s="8">
+        <f t="shared" si="0"/>
+        <v>8.6087977990091762E-3</v>
+      </c>
+      <c r="P17" s="8">
+        <f t="shared" si="0"/>
+        <v>9.9776435029914189E-3</v>
+      </c>
+      <c r="S17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T17" s="11">
+        <f>SUM(J19)</f>
+        <v>0.21385015109920591</v>
+      </c>
+      <c r="U17" s="11">
+        <f t="shared" ref="U17:AA17" si="4">SUM(K19)</f>
+        <v>0.21309843032184536</v>
+      </c>
+      <c r="V17" s="12">
+        <f t="shared" si="4"/>
+        <v>0.18317466557836887</v>
+      </c>
+      <c r="W17" s="12">
+        <f t="shared" si="4"/>
+        <v>0.18414317521528106</v>
+      </c>
+      <c r="X17" s="12">
+        <f t="shared" si="4"/>
+        <v>0.19419561840409508</v>
+      </c>
+      <c r="Y17" s="12">
+        <f t="shared" si="4"/>
+        <v>0.2125915585865194</v>
+      </c>
+      <c r="Z17" s="12">
+        <f t="shared" si="4"/>
+        <v>0.19889235587945878</v>
+      </c>
+      <c r="AA17" s="11"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A18" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18">
+        <v>42935241</v>
+      </c>
+      <c r="C18">
+        <v>46507063</v>
+      </c>
+      <c r="D18">
+        <v>48109566</v>
+      </c>
+      <c r="E18">
+        <v>51182533</v>
+      </c>
+      <c r="F18">
+        <v>52466807</v>
+      </c>
+      <c r="G18">
+        <v>56147628</v>
+      </c>
+      <c r="H18">
+        <v>58988458</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="2"/>
+        <v>0.14314324341812157</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.14055392187191471</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.12488757810060909</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.1225281287128429</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.10816802017449956</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13833339381825388</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.13547158975806173</v>
+      </c>
+      <c r="S18" t="s">
+        <v>249</v>
+      </c>
+      <c r="T18" s="11">
+        <f>SUM(J24:J29)</f>
+        <v>0.15380335947421789</v>
+      </c>
+      <c r="U18" s="11">
+        <f t="shared" ref="U18:AA18" si="5">SUM(K24:K29)</f>
+        <v>0.14498985832309591</v>
+      </c>
+      <c r="V18" s="12">
+        <f t="shared" si="5"/>
+        <v>0.16258089976707205</v>
+      </c>
+      <c r="W18" s="12">
+        <f t="shared" si="5"/>
+        <v>0.16532131789750665</v>
+      </c>
+      <c r="X18" s="12">
+        <f t="shared" si="5"/>
+        <v>0.19494999555271877</v>
+      </c>
+      <c r="Y18" s="12">
+        <f t="shared" si="5"/>
+        <v>0.1217192085990389</v>
+      </c>
+      <c r="Z18" s="12">
+        <f t="shared" si="5"/>
+        <v>0.12722757321048295</v>
+      </c>
+      <c r="AA18" s="11"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A19" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19">
+        <v>64143494</v>
+      </c>
+      <c r="C19">
+        <v>70510890</v>
+      </c>
+      <c r="D19">
+        <v>70563092</v>
+      </c>
+      <c r="E19">
+        <v>76920412</v>
+      </c>
+      <c r="F19">
+        <v>94194421</v>
+      </c>
+      <c r="G19">
+        <v>86287999</v>
+      </c>
+      <c r="H19">
+        <v>86603792</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="2"/>
+        <v>0.21385015109920591</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21309843032184536</v>
+      </c>
+      <c r="L19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18317466557836887</v>
+      </c>
+      <c r="M19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18414317521528106</v>
+      </c>
+      <c r="N19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19419561840409508</v>
+      </c>
+      <c r="O19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.2125915585865194</v>
+      </c>
+      <c r="P19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.19889235587945878</v>
+      </c>
+      <c r="S19" t="s">
+        <v>183</v>
+      </c>
+      <c r="T19" s="11">
+        <f>SUM(J15:J17,J20:J21,J23,J30)</f>
+        <v>0.32905289707096058</v>
+      </c>
+      <c r="U19" s="11">
+        <f t="shared" ref="U19:AA19" si="6">SUM(K15:K17,K20:K21,K23,K30)</f>
+        <v>0.33010551766071977</v>
+      </c>
+      <c r="V19" s="12">
+        <f t="shared" si="6"/>
+        <v>0.34177157413046189</v>
+      </c>
+      <c r="W19" s="12">
+        <f t="shared" si="6"/>
+        <v>0.35725916350255471</v>
+      </c>
+      <c r="X19" s="12">
+        <f t="shared" si="6"/>
+        <v>0.34662034677033776</v>
+      </c>
+      <c r="Y19" s="12">
+        <f t="shared" si="6"/>
+        <v>0.34155270186632813</v>
+      </c>
+      <c r="Z19" s="12">
+        <f t="shared" si="6"/>
+        <v>0.34957300071352382</v>
+      </c>
+      <c r="AA19" s="11"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A20" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20">
+        <v>2819017</v>
+      </c>
+      <c r="C20">
+        <v>3237099</v>
+      </c>
+      <c r="D20">
+        <v>3682217</v>
+      </c>
+      <c r="E20">
+        <v>3967285</v>
+      </c>
+      <c r="F20">
+        <v>4278457</v>
+      </c>
+      <c r="G20">
+        <v>4448238</v>
+      </c>
+      <c r="H20">
+        <v>4498254</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="2"/>
+        <v>9.3984155493810513E-3</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="0"/>
+        <v>9.783179813733953E-3</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" si="0"/>
+        <v>9.5586637212834238E-3</v>
+      </c>
+      <c r="M20" s="8">
+        <f t="shared" si="0"/>
+        <v>9.4974589694599709E-3</v>
+      </c>
+      <c r="N20" s="8">
+        <f t="shared" si="0"/>
+        <v>8.8206668092405318E-3</v>
+      </c>
+      <c r="O20" s="8">
+        <f t="shared" si="0"/>
+        <v>1.0959320651111423E-2</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="0"/>
+        <v>1.0330590782955543E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A21" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21">
+        <v>3588604</v>
+      </c>
+      <c r="C21">
+        <v>4186156</v>
+      </c>
+      <c r="D21">
+        <v>5279449</v>
+      </c>
+      <c r="E21">
+        <v>5517787</v>
+      </c>
+      <c r="F21">
+        <v>5784851</v>
+      </c>
+      <c r="G21">
+        <v>5260757</v>
+      </c>
+      <c r="H21">
+        <v>5475595</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="2"/>
+        <v>1.1964167521576152E-2</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="0"/>
+        <v>1.2651425512887084E-2</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3704916800032713E-2</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3209274260538282E-2</v>
+      </c>
+      <c r="N21" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1926319047287819E-2</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" si="0"/>
+        <v>1.2961159639070342E-2</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" si="0"/>
+        <v>1.2575130536914425E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A22" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22">
+        <v>48036452</v>
+      </c>
+      <c r="C22">
+        <v>56664661</v>
+      </c>
+      <c r="D22">
+        <v>72262163</v>
+      </c>
+      <c r="E22">
+        <v>71325060</v>
+      </c>
+      <c r="F22">
+        <v>75699690</v>
+      </c>
+      <c r="G22">
+        <v>75414946</v>
+      </c>
+      <c r="H22">
+        <v>82224721</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="2"/>
+        <v>0.16015034226962679</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.17125227484463021</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18758528242348818</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.17074821467181475</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.15606601703670211</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18580313712985969</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18883547814189486</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A23" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23">
+        <v>7417707</v>
+      </c>
+      <c r="C23">
+        <v>8765343</v>
+      </c>
+      <c r="D23">
+        <v>13183659</v>
+      </c>
+      <c r="E23">
+        <v>23153440</v>
+      </c>
+      <c r="F23">
+        <v>29370396</v>
+      </c>
+      <c r="G23">
+        <v>16801462</v>
+      </c>
+      <c r="H23">
+        <v>15762368</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="2"/>
+        <v>2.4730142744634982E-2</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="0"/>
+        <v>2.6490671647068628E-2</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" si="0"/>
+        <v>3.4223448264203794E-2</v>
+      </c>
+      <c r="M23" s="8">
+        <f t="shared" si="0"/>
+        <v>5.5428043712980851E-2</v>
+      </c>
+      <c r="N23" s="8">
+        <f t="shared" si="0"/>
+        <v>6.0551380362464997E-2</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" si="0"/>
+        <v>4.1394504850114547E-2</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="0"/>
+        <v>3.6199506203596639E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A24" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24">
+        <v>9102720</v>
+      </c>
+      <c r="C24">
+        <v>9421392</v>
+      </c>
+      <c r="D24">
+        <v>10278984</v>
+      </c>
+      <c r="E24">
+        <v>7206629</v>
+      </c>
+      <c r="F24">
+        <v>6839900</v>
+      </c>
+      <c r="G24">
+        <v>9194983</v>
+      </c>
+      <c r="H24">
+        <v>9251480</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="2"/>
+        <v>3.03478642341149E-2</v>
+      </c>
+      <c r="K24" s="8">
+        <f t="shared" si="0"/>
+        <v>2.8473386829279721E-2</v>
+      </c>
+      <c r="L24" s="8">
+        <f t="shared" si="0"/>
+        <v>2.6683205105090976E-2</v>
+      </c>
+      <c r="M24" s="8">
+        <f t="shared" si="0"/>
+        <v>1.7252267794126294E-2</v>
+      </c>
+      <c r="N24" s="8">
+        <f t="shared" si="0"/>
+        <v>1.4101457349816609E-2</v>
+      </c>
+      <c r="O24" s="8">
+        <f t="shared" si="0"/>
+        <v>2.265408619739287E-2</v>
+      </c>
+      <c r="P24" s="8">
+        <f t="shared" si="0"/>
+        <v>2.1246744629515705E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A25" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B25">
+        <v>7212104</v>
+      </c>
+      <c r="C25">
+        <v>8707407</v>
+      </c>
+      <c r="D25">
+        <v>20342104</v>
+      </c>
+      <c r="E25">
+        <v>28300984</v>
+      </c>
+      <c r="F25">
+        <v>54720624</v>
+      </c>
+      <c r="G25">
+        <v>11439996</v>
+      </c>
+      <c r="H25">
+        <v>11666777</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="2"/>
+        <v>2.4044675990727717E-2</v>
+      </c>
+      <c r="K25" s="8">
+        <f t="shared" si="0"/>
+        <v>2.6315577123951328E-2</v>
+      </c>
+      <c r="L25" s="8">
+        <f t="shared" si="0"/>
+        <v>5.2806049051257554E-2</v>
+      </c>
+      <c r="M25" s="8">
+        <f t="shared" si="0"/>
+        <v>6.7750976886042494E-2</v>
+      </c>
+      <c r="N25" s="8">
+        <f t="shared" si="0"/>
+        <v>0.11281459458345167</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="0"/>
+        <v>2.8185223994631602E-2</v>
+      </c>
+      <c r="P25" s="8">
+        <f t="shared" si="0"/>
+        <v>2.6793662372777909E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A26" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26">
+        <v>18802026</v>
+      </c>
+      <c r="C26">
+        <v>17501589</v>
+      </c>
+      <c r="D26">
+        <v>18321882</v>
+      </c>
+      <c r="E26">
+        <v>18172496</v>
+      </c>
+      <c r="F26">
+        <v>16663254</v>
+      </c>
+      <c r="G26">
+        <v>12691950</v>
+      </c>
+      <c r="H26">
+        <v>17055764</v>
+      </c>
+      <c r="J26" s="8">
+        <f t="shared" si="2"/>
+        <v>6.268470659037062E-2</v>
+      </c>
+      <c r="K26" s="8">
+        <f t="shared" si="0"/>
+        <v>5.2893406168012844E-2</v>
+      </c>
+      <c r="L26" s="8">
+        <f t="shared" si="0"/>
+        <v>4.7561756620817242E-2</v>
+      </c>
+      <c r="M26" s="8">
+        <f t="shared" si="0"/>
+        <v>4.3503941645905306E-2</v>
+      </c>
+      <c r="N26" s="8">
+        <f t="shared" si="0"/>
+        <v>3.4353742831059082E-2</v>
+      </c>
+      <c r="O26" s="8">
+        <f t="shared" si="0"/>
+        <v>3.1269718422861734E-2</v>
+      </c>
+      <c r="P26" s="8">
+        <f t="shared" si="0"/>
+        <v>3.9169890889813014E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A27" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27">
+        <v>348072</v>
+      </c>
+      <c r="C27">
+        <v>354568</v>
+      </c>
+      <c r="D27">
+        <v>434555</v>
+      </c>
+      <c r="E27">
+        <v>583767</v>
+      </c>
+      <c r="F27">
+        <v>1025036</v>
+      </c>
+      <c r="G27">
+        <v>963709</v>
+      </c>
+      <c r="H27">
+        <v>899859</v>
+      </c>
+      <c r="J27" s="8">
+        <f t="shared" si="2"/>
+        <v>1.1604489427002964E-3</v>
+      </c>
+      <c r="K27" s="8">
+        <f t="shared" si="0"/>
+        <v>1.0715775143719795E-3</v>
+      </c>
+      <c r="L27" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1280609245469017E-3</v>
+      </c>
+      <c r="M27" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3975056317417928E-3</v>
+      </c>
+      <c r="N27" s="8">
+        <f t="shared" si="0"/>
+        <v>2.1132620997421918E-3</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" si="0"/>
+        <v>2.3743324762213573E-3</v>
+      </c>
+      <c r="P27" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0665963041125715E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A28" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28">
+        <v>4510928</v>
+      </c>
+      <c r="C28">
+        <v>5549322</v>
+      </c>
+      <c r="D28">
+        <v>6449132</v>
+      </c>
+      <c r="E28">
+        <v>7392871</v>
+      </c>
+      <c r="F28">
+        <v>7534780</v>
+      </c>
+      <c r="G28">
+        <v>7088677</v>
+      </c>
+      <c r="H28">
+        <v>8756881</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="2"/>
+        <v>1.5039134512966174E-2</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="0"/>
+        <v>1.6771193890057032E-2</v>
+      </c>
+      <c r="L28" s="8">
+        <f t="shared" si="0"/>
+        <v>1.6741295823186959E-2</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="0"/>
+        <v>1.7698120752355957E-2</v>
+      </c>
+      <c r="N28" s="8">
+        <f t="shared" si="0"/>
+        <v>1.5534054417498966E-2</v>
+      </c>
+      <c r="O28" s="8">
+        <f t="shared" si="0"/>
+        <v>1.7464686969347991E-2</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0110859490379714E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A29" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29">
+        <v>6156850</v>
+      </c>
+      <c r="C29">
+        <v>6440566</v>
+      </c>
+      <c r="D29">
+        <v>6803243</v>
+      </c>
+      <c r="E29">
+        <v>7401386</v>
+      </c>
+      <c r="F29">
+        <v>7776737</v>
+      </c>
+      <c r="G29">
+        <v>8024843</v>
+      </c>
+      <c r="H29">
+        <v>7768001</v>
+      </c>
+      <c r="J29" s="8">
+        <f t="shared" si="2"/>
+        <v>2.0526529203338157E-2</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.946471679742301E-2</v>
+      </c>
+      <c r="L29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.7660532242172421E-2</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.7718505187334775E-2</v>
+      </c>
+      <c r="N29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.6032884271150273E-2</v>
+      </c>
+      <c r="O29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.9771160538583354E-2</v>
+      </c>
+      <c r="P29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.783981952388403E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30">
+        <v>567000</v>
+      </c>
+      <c r="C30">
+        <v>580000</v>
+      </c>
+      <c r="D30">
+        <v>550000</v>
+      </c>
+      <c r="E30">
+        <v>550000</v>
+      </c>
+      <c r="F30">
+        <v>576000</v>
+      </c>
+      <c r="G30">
+        <v>607200</v>
+      </c>
+      <c r="H30">
+        <v>638300</v>
+      </c>
+      <c r="J30" s="8">
+        <f>B30/B$14</f>
+        <v>1.8903403620833276E-3</v>
+      </c>
+      <c r="K30" s="8">
+        <f t="shared" si="0"/>
+        <v>1.7528794429721465E-3</v>
+      </c>
+      <c r="L30" s="8">
+        <f t="shared" si="0"/>
+        <v>1.4277444937943319E-3</v>
+      </c>
+      <c r="M30" s="8">
+        <f t="shared" si="0"/>
+        <v>1.3166693174810945E-3</v>
+      </c>
+      <c r="N30" s="8">
+        <f t="shared" si="0"/>
+        <v>1.1875085064831893E-3</v>
+      </c>
+      <c r="O30" s="8">
+        <f t="shared" si="0"/>
+        <v>1.4959854889407573E-3</v>
+      </c>
+      <c r="P30" s="8">
+        <f t="shared" si="0"/>
+        <v>1.4659056817957641E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F301B4E9-04FF-49B8-991D-45F22283AB5C}">
+  <dimension ref="A1:AK19"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A2" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="B2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A3" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A4" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="O4" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q4" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="S4" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="T4" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="U4" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="W4" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="X4" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y4" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="Z4" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="AA4" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC4" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="AD4" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="AE4" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="AF4" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="AG4" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="AH4" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="AI4" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="AJ4" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="AK4" s="15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A5" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="Y5" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z5" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="AA5" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="AB5" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="AD5" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="AE5" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="AI5" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="AJ5" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="AK5" s="14" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A6" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="V6" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="W6" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="X6" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y6" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z6" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="AA6" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB6" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="AC6" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AD6" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="AE6" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="AF6" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG6" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="AH6" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="AI6" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="AJ6" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="AK6" s="14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A7" s="16"/>
+      <c r="B7" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="W7" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="X7" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="Y7" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="Z7" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA7" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC7" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="AD7" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="AE7" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AF7" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AG7" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="AH7" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI7" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="AJ7" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="AK7" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A8" s="16"/>
+      <c r="B8" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q8" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="X8" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y8" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="Z8" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA8" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="AB8" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC8" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD8" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="AE8" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AF8" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="AG8" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="AH8" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="AI8" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="AJ8" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="AK8" s="14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A9" s="16"/>
+      <c r="B9" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="X9" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y9" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z9" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA9" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB9" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="AD9" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE9" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="AF9" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="AG9" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="AH9" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="AI9" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AK9" s="14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A10" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A12" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="C14" t="str">
+        <f>C4</f>
+        <v>1990</v>
+      </c>
+      <c r="D14" t="str">
+        <f>H4</f>
+        <v>1995</v>
+      </c>
+      <c r="E14" t="str">
+        <f>M4</f>
+        <v>2000</v>
+      </c>
+      <c r="F14" t="str">
+        <f>R4</f>
+        <v>2005</v>
+      </c>
+      <c r="G14" t="str">
+        <f>W4</f>
+        <v>2010</v>
+      </c>
+      <c r="H14" t="str">
+        <f>AB4</f>
+        <v>2015</v>
+      </c>
+      <c r="I14" t="str">
+        <f>AG4</f>
+        <v>2020</v>
+      </c>
+      <c r="J14" t="str">
+        <f>AH4</f>
+        <v>2021</v>
+      </c>
+      <c r="K14" t="str">
+        <f>AI4</f>
+        <v>2022</v>
+      </c>
+      <c r="L14" t="str">
+        <f>AJ4</f>
+        <v>2023</v>
+      </c>
+      <c r="M14" t="str">
+        <f>AK4</f>
+        <v>2024 p)</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A15" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" t="str">
+        <f t="shared" ref="C15:C19" si="0">C5</f>
+        <v>206.7</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" ref="D15:D19" si="1">H5</f>
+        <v>452.2</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" ref="E15:E19" si="2">M5</f>
+        <v>675.7</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" ref="F15:F19" si="3">R5</f>
+        <v>995.2</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" ref="G15:G19" si="4">W5</f>
+        <v>1,379.5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" ref="H15:H19" si="5">AB5</f>
+        <v>1,740.8</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" ref="I15:M15" si="6">AG5</f>
+        <v>2,058.5</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="6"/>
+        <v>2,221.9</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="6"/>
+        <v>2,323.8</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="6"/>
+        <v>2,408.7</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="6"/>
+        <v>2,556.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A16" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>33.2</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="1"/>
+        <v>72.1</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="2"/>
+        <v>113.5</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="3"/>
+        <v>163.4</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="4"/>
+        <v>226.9</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="5"/>
+        <v>288.9</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" ref="I16:M16" si="7">AG6</f>
+        <v>387.6</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="7"/>
+        <v>456.9</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="7"/>
+        <v>514.5</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="7"/>
+        <v>456.5</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="7"/>
+        <v>450.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" s="16"/>
+      <c r="B17" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>16.1</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="1"/>
+        <v>15.9</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="2"/>
+        <v>16.8</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="3"/>
+        <v>16.4</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="4"/>
+        <v>16.4</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="5"/>
+        <v>16.6</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" ref="I17:M17" si="8">AG7</f>
+        <v>18.8</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="8"/>
+        <v>20.6</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="8"/>
+        <v>22.1</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="8"/>
+        <v>19.0</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="8"/>
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A18" s="16"/>
+      <c r="B18" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>26.8</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="1"/>
+        <v>56.8</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="2"/>
+        <v>92.9</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="3"/>
+        <v>127.5</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="4"/>
+        <v>177.7</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="5"/>
+        <v>217.9</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" ref="I18:M18" si="9">AG8</f>
+        <v>285.5</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="9"/>
+        <v>344.1</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="9"/>
+        <v>395.9</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="9"/>
+        <v>344.1</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="9"/>
+        <v>336.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" s="16"/>
+      <c r="B19" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>6.4</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="1"/>
+        <v>15.3</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="2"/>
+        <v>20.6</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="3"/>
+        <v>36.0</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="4"/>
+        <v>49.2</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="5"/>
+        <v>71.0</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" ref="I19:M19" si="10">AG9</f>
+        <v>102.0</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="10"/>
+        <v>112.8</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="10"/>
+        <v>118.6</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="10"/>
+        <v>112.5</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="10"/>
+        <v>114.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{A6873029-20B4-47D3-A259-54AD06EADEFD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>